--- a/outputs/cv_results.xlsx
+++ b/outputs/cv_results.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="k_8" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="k_8" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -654,58 +654,58 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1342</v>
+        <v>0.1442</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6817</v>
+        <v>0.6888</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7544999999999999</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2099</v>
+        <v>0.1931</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8584000000000001</v>
+        <v>0.8685</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5945</v>
+        <v>0.5921</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5722</v>
+        <v>0.5715</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4094</v>
+        <v>0.4099</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7563</v>
+        <v>0.7558</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1228</v>
+        <v>0.1384</v>
       </c>
       <c r="L4" t="n">
-        <v>0.119</v>
+        <v>0.1321</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2505</v>
+        <v>0.281</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0883</v>
+        <v>0.1067</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1418</v>
+        <v>0.1564</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0139</v>
+        <v>0.0138</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0223</v>
+        <v>0.0221</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0167</v>
+        <v>0.0215</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0147</v>
+        <v>0.0148</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cv_results.xlsx
+++ b/outputs/cv_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,184 +528,306 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DTR</t>
+          <t>ADA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0949</v>
+        <v>0.1794</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6659</v>
+        <v>0.6625</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7030999999999999</v>
+        <v>0.7341</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2465</v>
+        <v>0.242</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8322000000000001</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6431</v>
+        <v>0.5291</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6403</v>
+        <v>0.4673</v>
       </c>
       <c r="I2" t="n">
-        <v>0.34</v>
+        <v>0.5178</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7997</v>
+        <v>0.6834</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1002</v>
+        <v>0.1584</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1028</v>
+        <v>0.1365</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1906</v>
+        <v>0.2914</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1427</v>
+        <v>0.1331</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1101</v>
+        <v>0.1681</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0234</v>
+        <v>0.0136</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0477</v>
+        <v>0.0209</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0277</v>
+        <v>0.0122</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0301</v>
+        <v>0.0154</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1515</v>
+        <v>0.1482</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6643</v>
+        <v>0.6625</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7355</v>
+        <v>0.7345</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2378</v>
+        <v>0.2397</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8431999999999999</v>
+        <v>0.8434</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6169</v>
+        <v>0.5725</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6315</v>
+        <v>0.5407</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3484</v>
+        <v>0.4417</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7944</v>
+        <v>0.7352</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1119</v>
+        <v>0.1348</v>
       </c>
       <c r="L3" t="n">
-        <v>0.139</v>
+        <v>0.1372</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2915</v>
+        <v>0.2796</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1461</v>
+        <v>0.123</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1674</v>
+        <v>0.1625</v>
       </c>
       <c r="P3" t="n">
-        <v>0.019</v>
+        <v>0.0107</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0364</v>
+        <v>0.0182</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0271</v>
+        <v>0.0197</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0233</v>
+        <v>0.0126</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>DTR</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.0926</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.6621</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.7024</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.2467</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.832</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6335</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.6229</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.3578</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.7887</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.1852</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.1385</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.1072</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.0263</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.0511</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.0354</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.0329</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.1445</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.6576</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.7232</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.8366</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5807</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.5619</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.4201</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.7494</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.1344</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.1366</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.2844</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.1629</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.0309</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.0237</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.0209</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>XGB</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>0.1342</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.6817</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.7544999999999999</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.2099</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.8584000000000001</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.5945</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.5722</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.4094</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.7563</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.1228</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.119</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.2505</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.0883</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.1418</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.0139</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.0223</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.0167</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.0147</v>
+      <c r="B6" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.6783</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.7473</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.8534</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.5927</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.5693</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.4123</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.7544</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.1222</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.1222</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.2587</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.1476</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.0131</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.0201</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.0133</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cv_results.xlsx
+++ b/outputs/cv_results.xlsx
@@ -532,58 +532,58 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1794</v>
+        <v>0.1784</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6625</v>
+        <v>0.6553</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7341</v>
+        <v>0.7292</v>
       </c>
       <c r="E2" t="n">
-        <v>0.242</v>
+        <v>0.2454</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8421999999999999</v>
+        <v>0.8398</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5291</v>
+        <v>0.5167</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4673</v>
+        <v>0.4535</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5178</v>
+        <v>0.532</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6834</v>
+        <v>0.6733</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1584</v>
+        <v>0.1685</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1365</v>
+        <v>0.1336</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2914</v>
+        <v>0.2909</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1331</v>
+        <v>0.1305</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1681</v>
+        <v>0.1651</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0136</v>
+        <v>0.0135</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0209</v>
+        <v>0.0229</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0122</v>
+        <v>0.0156</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0154</v>
+        <v>0.0173</v>
       </c>
     </row>
     <row r="3">
@@ -593,58 +593,58 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1482</v>
+        <v>0.1552</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6625</v>
+        <v>0.6679</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7345</v>
+        <v>0.7445000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2397</v>
+        <v>0.2299</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8434</v>
+        <v>0.8494</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5725</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5407</v>
+        <v>0.5779</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4417</v>
+        <v>0.4037</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7352</v>
+        <v>0.76</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1348</v>
+        <v>0.1213</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1372</v>
+        <v>0.1408</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2796</v>
+        <v>0.2816</v>
       </c>
       <c r="N3" t="n">
-        <v>0.123</v>
+        <v>0.1116</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1625</v>
+        <v>0.1619</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0107</v>
+        <v>0.0164</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0182</v>
+        <v>0.0313</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0197</v>
+        <v>0.0199</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0126</v>
+        <v>0.0208</v>
       </c>
     </row>
     <row r="4">
@@ -654,58 +654,58 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0926</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6621</v>
+        <v>0.6958</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7024</v>
+        <v>0.748</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2467</v>
+        <v>0.2046</v>
       </c>
       <c r="F4" t="n">
-        <v>0.832</v>
+        <v>0.861</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6335</v>
+        <v>0.6161</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6229</v>
+        <v>0.6099</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3578</v>
+        <v>0.371</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7887</v>
+        <v>0.7805</v>
       </c>
       <c r="K4" t="n">
-        <v>0.107</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>0.089</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1852</v>
+        <v>0.1576</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1385</v>
+        <v>0.1475</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1072</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0263</v>
+        <v>0.0249</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0511</v>
+        <v>0.044</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0354</v>
+        <v>0.0312</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0329</v>
+        <v>0.0286</v>
       </c>
     </row>
     <row r="5">
@@ -715,58 +715,58 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1445</v>
+        <v>0.145</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6576</v>
+        <v>0.6572</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7232</v>
+        <v>0.7231</v>
       </c>
       <c r="E5" t="n">
-        <v>0.249</v>
+        <v>0.2492</v>
       </c>
       <c r="F5" t="n">
         <v>0.8366</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5807</v>
+        <v>0.5821</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5619</v>
+        <v>0.5646</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4201</v>
+        <v>0.4173</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7494</v>
+        <v>0.7512</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1344</v>
+        <v>0.1331</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1366</v>
+        <v>0.1367</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2844</v>
+        <v>0.2848</v>
       </c>
       <c r="N5" t="n">
-        <v>0.141</v>
+        <v>0.1415</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1629</v>
+        <v>0.1632</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0164</v>
+        <v>0.0167</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0309</v>
+        <v>0.0313</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0237</v>
+        <v>0.0236</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0209</v>
+        <v>0.0212</v>
       </c>
     </row>
     <row r="6">
@@ -776,58 +776,58 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.137</v>
+        <v>0.138</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6783</v>
+        <v>0.6711</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7473</v>
+        <v>0.7381</v>
       </c>
       <c r="E6" t="n">
-        <v>0.221</v>
+        <v>0.2306</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8534</v>
+        <v>0.8474</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5927</v>
+        <v>0.5904</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5693</v>
+        <v>0.5753</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4123</v>
+        <v>0.4062</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7544</v>
+        <v>0.7583</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1222</v>
+        <v>0.1223</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1222</v>
+        <v>0.1267</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2587</v>
+        <v>0.2624</v>
       </c>
       <c r="N6" t="n">
-        <v>0.089</v>
+        <v>0.1112</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1476</v>
+        <v>0.1511</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0131</v>
+        <v>0.0152</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0201</v>
+        <v>0.0254</v>
       </c>
       <c r="R6" t="n">
-        <v>0.016</v>
+        <v>0.0181</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0133</v>
+        <v>0.0169</v>
       </c>
     </row>
   </sheetData>
